--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61392-2024 artfynd.xlsx
+++ b/artfynd/A 61392-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129083686</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
